--- a/data/trans_orig/P2C_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2007</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66759</t>
+          <t>67333</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91343</t>
+          <t>90275</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>97387</t>
+          <t>97402</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122344</t>
+          <t>120851</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>170077</t>
+          <t>169319</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>205280</t>
+          <t>205532</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,67%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55584</t>
+          <t>56652</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80168</t>
+          <t>79594</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43719</t>
+          <t>45212</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68676</t>
+          <t>68661</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107711</t>
+          <t>107459</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>142914</t>
+          <t>143672</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,9%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67750</t>
+          <t>66659</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>96937</t>
+          <t>97150</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>125286</t>
+          <t>125518</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>161939</t>
+          <t>162344</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>198734</t>
+          <t>199134</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>248165</t>
+          <t>249505</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,97%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>189022</t>
+          <t>188809</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>218209</t>
+          <t>219300</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>192296</t>
+          <t>191891</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>228949</t>
+          <t>228717</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>392029</t>
+          <t>390689</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>441460</t>
+          <t>441060</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,89%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63981</t>
+          <t>61679</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90137</t>
+          <t>89038</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94949</t>
+          <t>94443</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>124072</t>
+          <t>124395</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164797</t>
+          <t>163911</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>205444</t>
+          <t>204262</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,08%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>100027</t>
+          <t>101126</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126183</t>
+          <t>128485</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>101937</t>
+          <t>101614</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131060</t>
+          <t>131566</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>210729</t>
+          <t>211911</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>251376</t>
+          <t>252262</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,61%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79151</t>
+          <t>78679</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107420</t>
+          <t>107592</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105648</t>
+          <t>105515</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>136812</t>
+          <t>135127</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>191945</t>
+          <t>192012</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>232210</t>
+          <t>233623</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,58%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91689</t>
+          <t>91517</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119958</t>
+          <t>120430</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108429</t>
+          <t>110114</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>139593</t>
+          <t>139726</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>212140</t>
+          <t>210727</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>252405</t>
+          <t>252338</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,79%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23286</t>
+          <t>23128</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41850</t>
+          <t>41869</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42097</t>
+          <t>42794</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66126</t>
+          <t>66081</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72285</t>
+          <t>70949</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103216</t>
+          <t>102189</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66239</t>
+          <t>66220</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84803</t>
+          <t>84961</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83565</t>
+          <t>83610</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107594</t>
+          <t>106897</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>154564</t>
+          <t>155591</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>185495</t>
+          <t>186831</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,48%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58268</t>
+          <t>57163</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82622</t>
+          <t>81730</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58721</t>
+          <t>59018</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85306</t>
+          <t>85156</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>124285</t>
+          <t>125627</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>160018</t>
+          <t>160423</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,07%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>79742</t>
+          <t>80634</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>104096</t>
+          <t>105201</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>93173</t>
+          <t>93323</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>119758</t>
+          <t>119461</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>180825</t>
+          <t>180420</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216558</t>
+          <t>215216</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,14%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105545</t>
+          <t>105573</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>141581</t>
+          <t>141429</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>209798</t>
+          <t>209874</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>252638</t>
+          <t>249844</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>323748</t>
+          <t>323198</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>381183</t>
+          <t>380874</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,94%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>209930</t>
+          <t>210082</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>245966</t>
+          <t>245938</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>190296</t>
+          <t>193090</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>233136</t>
+          <t>233060</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>413262</t>
+          <t>413571</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>470697</t>
+          <t>471247</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>59,32%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>133714</t>
+          <t>134109</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>176059</t>
+          <t>175516</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>199092</t>
+          <t>199026</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>241764</t>
+          <t>243422</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>346324</t>
+          <t>345990</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>407419</t>
+          <t>406147</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,42%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>290043</t>
+          <t>290586</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>332388</t>
+          <t>331993</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>296948</t>
+          <t>295290</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>339620</t>
+          <t>339686</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>597395</t>
+          <t>598667</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>658490</t>
+          <t>658824</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,57%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>663183</t>
+          <t>666019</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>748468</t>
+          <t>749273</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1010970</t>
+          <t>1015276</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1103813</t>
+          <t>1109391</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1698885</t>
+          <t>1698777</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1829024</t>
+          <t>1830993</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,48%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1161758</t>
+          <t>1160953</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1247043</t>
+          <t>1244207</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1197549</t>
+          <t>1191971</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1290392</t>
+          <t>1286086</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2382564</t>
+          <t>2380595</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2512703</t>
+          <t>2512811</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2012</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2012 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77210</t>
+          <t>77391</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>103856</t>
+          <t>104406</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>125827</t>
+          <t>127593</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>154262</t>
+          <t>155158</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>211763</t>
+          <t>209310</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>251305</t>
+          <t>248189</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,23%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73868</t>
+          <t>73318</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100514</t>
+          <t>100333</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54421</t>
+          <t>53525</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82856</t>
+          <t>81090</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>135103</t>
+          <t>138219</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174645</t>
+          <t>177098</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,83%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>113622</t>
+          <t>116122</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>149667</t>
+          <t>151672</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>196312</t>
+          <t>197082</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>233189</t>
+          <t>234348</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>320991</t>
+          <t>322702</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>374199</t>
+          <t>377229</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,87%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>167155</t>
+          <t>165150</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>203200</t>
+          <t>200700</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>125222</t>
+          <t>124063</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>162099</t>
+          <t>161329</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>301033</t>
+          <t>298003</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>354241</t>
+          <t>352530</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,21%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92150</t>
+          <t>91208</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120150</t>
+          <t>120667</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>125210</t>
+          <t>125392</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>156441</t>
+          <t>155491</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>228196</t>
+          <t>226384</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>268789</t>
+          <t>268734</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,42%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85045</t>
+          <t>84528</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>113045</t>
+          <t>113987</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83158</t>
+          <t>84108</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114389</t>
+          <t>114207</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>176005</t>
+          <t>176060</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>216598</t>
+          <t>218410</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>49,1%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>101251</t>
+          <t>100612</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>134881</t>
+          <t>132703</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>166204</t>
+          <t>164483</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>200131</t>
+          <t>197335</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>274543</t>
+          <t>274659</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>321419</t>
+          <t>322726</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>60,16%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108885</t>
+          <t>111063</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>142515</t>
+          <t>143154</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>92540</t>
+          <t>95336</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126467</t>
+          <t>128188</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>215018</t>
+          <t>213711</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>261894</t>
+          <t>261778</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,8%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43806</t>
+          <t>44270</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69365</t>
+          <t>68567</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>82300</t>
+          <t>81096</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107819</t>
+          <t>107771</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>134107</t>
+          <t>133288</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169860</t>
+          <t>169802</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,49%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75697</t>
+          <t>76495</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101256</t>
+          <t>100792</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58722</t>
+          <t>58770</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84241</t>
+          <t>85445</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>141743</t>
+          <t>141801</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>177496</t>
+          <t>178315</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,23%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73036</t>
+          <t>73674</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>100395</t>
+          <t>101120</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>103051</t>
+          <t>102838</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>131353</t>
+          <t>132480</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>184487</t>
+          <t>185589</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>224870</t>
+          <t>224811</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,11%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75563</t>
+          <t>74838</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102922</t>
+          <t>102284</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>73003</t>
+          <t>71876</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101305</t>
+          <t>101518</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>155444</t>
+          <t>155503</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>195827</t>
+          <t>194725</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,2%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>222121</t>
+          <t>221890</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>259559</t>
+          <t>262116</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>272369</t>
+          <t>272930</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>314767</t>
+          <t>314118</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>506290</t>
+          <t>506426</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>565987</t>
+          <t>563382</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,0%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>137379</t>
+          <t>134822</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>174817</t>
+          <t>175048</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>141844</t>
+          <t>142493</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>184242</t>
+          <t>183681</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>287562</t>
+          <t>290167</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>347259</t>
+          <t>347123</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,67%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>199617</t>
+          <t>200420</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>244823</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>338646</t>
+          <t>339406</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>386343</t>
+          <t>388259</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>552931</t>
+          <t>548516</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>618750</t>
+          <t>617897</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>57,97%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>231037</t>
+          <t>231450</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>276243</t>
+          <t>275440</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>203617</t>
+          <t>201701</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>251314</t>
+          <t>250554</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>447070</t>
+          <t>447923</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>512889</t>
+          <t>517304</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,54%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1006826</t>
+          <t>1006836</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1101905</t>
+          <t>1105466</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1502778</t>
+          <t>1497883</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1597594</t>
+          <t>1594913</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2530825</t>
+          <t>2525671</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2673145</t>
+          <t>2665308</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,27%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1035421</t>
+          <t>1031860</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1130500</t>
+          <t>1130490</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>919236</t>
+          <t>921917</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1014052</t>
+          <t>1018947</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1981011</t>
+          <t>1988848</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2123331</t>
+          <t>2128485</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,73%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2016</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2016 (tasa de respuesta: 94,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65135</t>
+          <t>65824</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91474</t>
+          <t>92045</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>85592</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114939</t>
+          <t>115192</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>158876</t>
+          <t>158604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199052</t>
+          <t>199098</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,28%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81987</t>
+          <t>81416</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>108326</t>
+          <t>107637</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85312</t>
+          <t>85059</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113849</t>
+          <t>114659</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174660</t>
+          <t>174614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>214836</t>
+          <t>215108</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,56%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85677</t>
+          <t>85510</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>117741</t>
+          <t>117640</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136143</t>
+          <t>137368</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>174403</t>
+          <t>173767</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>233091</t>
+          <t>232851</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>280123</t>
+          <t>282968</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,41%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>144480</t>
+          <t>144581</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>176544</t>
+          <t>176711</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>147918</t>
+          <t>148554</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>186178</t>
+          <t>184953</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>304419</t>
+          <t>301574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>351451</t>
+          <t>351691</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,17%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56781</t>
+          <t>56359</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82026</t>
+          <t>80409</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77318</t>
+          <t>76880</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105149</t>
+          <t>105770</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140996</t>
+          <t>142078</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>179594</t>
+          <t>179207</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,97%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95623</t>
+          <t>97240</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>120868</t>
+          <t>121290</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>107007</t>
+          <t>106386</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>134838</t>
+          <t>135276</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>210211</t>
+          <t>210598</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>248809</t>
+          <t>247727</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,55%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52560</t>
+          <t>51882</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80434</t>
+          <t>78917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>107221</t>
+          <t>107591</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>140912</t>
+          <t>141101</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170237</t>
+          <t>166003</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>211260</t>
+          <t>211632</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,33%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>111082</t>
+          <t>112599</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>138956</t>
+          <t>139634</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>114745</t>
+          <t>114556</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>148436</t>
+          <t>148066</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>235913</t>
+          <t>235541</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>276936</t>
+          <t>281170</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,88%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66910</t>
+          <t>67258</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>88540</t>
+          <t>89818</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76793</t>
+          <t>76573</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98814</t>
+          <t>99425</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>150872</t>
+          <t>150219</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>183119</t>
+          <t>183652</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,75%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45262</t>
+          <t>43984</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66892</t>
+          <t>66544</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46704</t>
+          <t>46093</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68725</t>
+          <t>68945</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>96201</t>
+          <t>95668</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>128448</t>
+          <t>129101</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,22%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52742</t>
+          <t>53106</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77339</t>
+          <t>76108</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58463</t>
+          <t>58038</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85520</t>
+          <t>84300</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>118348</t>
+          <t>118866</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>153837</t>
+          <t>155783</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,79%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>83882</t>
+          <t>85113</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>108479</t>
+          <t>108115</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>86197</t>
+          <t>87417</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>113254</t>
+          <t>113679</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>179100</t>
+          <t>177154</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>214589</t>
+          <t>214071</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,3%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>126001</t>
+          <t>123452</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>162804</t>
+          <t>162455</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>198851</t>
+          <t>199235</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>244515</t>
+          <t>242667</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>334777</t>
+          <t>336338</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>391165</t>
+          <t>393226</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>50,17%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>177474</t>
+          <t>177823</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>214277</t>
+          <t>216826</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>198987</t>
+          <t>200835</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>244651</t>
+          <t>244267</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>392615</t>
+          <t>390554</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>449003</t>
+          <t>447442</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,09%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>217488</t>
+          <t>216158</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>259485</t>
+          <t>259990</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>319137</t>
+          <t>320062</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>367409</t>
+          <t>369165</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>549349</t>
+          <t>548823</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>615329</t>
+          <t>613389</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>58,94%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>197295</t>
+          <t>196790</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>239292</t>
+          <t>240622</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>216490</t>
+          <t>214734</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>264762</t>
+          <t>263837</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>425350</t>
+          <t>427290</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>491330</t>
+          <t>491856</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,26%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>794075</t>
+          <t>797796</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>880538</t>
+          <t>881605</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1142237</t>
+          <t>1146440</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1246758</t>
+          <t>1247762</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1966355</t>
+          <t>1960395</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2099250</t>
+          <t>2097694</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,57%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1016390</t>
+          <t>1015323</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1102853</t>
+          <t>1099132</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1088262</t>
+          <t>1087258</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1192783</t>
+          <t>1188580</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2132698</t>
+          <t>2134254</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2265593</t>
+          <t>2271553</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,68%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2023</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19717</t>
+          <t>19706</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9232</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20492</t>
+          <t>20467</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18003</t>
+          <t>17986</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34676</t>
+          <t>34553</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>291726</t>
+          <t>291737</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>305427</t>
+          <t>305302</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269143</t>
+          <t>269168</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280226</t>
+          <t>280403</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>566401</t>
+          <t>566524</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>583074</t>
+          <t>583091</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18922</t>
+          <t>18146</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42593</t>
+          <t>42187</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50213</t>
+          <t>51226</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79222</t>
+          <t>78400</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75878</t>
+          <t>74728</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112214</t>
+          <t>112304</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>475797</t>
+          <t>476203</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499468</t>
+          <t>500244</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>435747</t>
+          <t>436569</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>464756</t>
+          <t>463743</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>921145</t>
+          <t>921055</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>957481</t>
+          <t>958631</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>11214</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26548</t>
+          <t>26374</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17426</t>
+          <t>16862</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33981</t>
+          <t>33875</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>32620</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53615</t>
+          <t>54259</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>289502</t>
+          <t>289676</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>305031</t>
+          <t>304836</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>315147</t>
+          <t>315253</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>331702</t>
+          <t>332266</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>611563</t>
+          <t>610919</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>633201</t>
+          <t>632558</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16739</t>
+          <t>16717</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42106</t>
+          <t>39915</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27830</t>
+          <t>28190</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64646</t>
+          <t>65245</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53361</t>
+          <t>51367</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95946</t>
+          <t>94883</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>270451</t>
+          <t>272642</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>295818</t>
+          <t>295840</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>411072</t>
+          <t>410473</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>447888</t>
+          <t>447528</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>692328</t>
+          <t>693391</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>734913</t>
+          <t>736907</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,48%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23128</t>
+          <t>24743</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19193</t>
+          <t>19971</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16639</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36054</t>
+          <t>37968</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>155614</t>
+          <t>153999</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169344</t>
+          <t>169766</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>239586</t>
+          <t>238808</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>252053</t>
+          <t>252545</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>401467</t>
+          <t>399553</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>420882</t>
+          <t>419557</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21642</t>
+          <t>21625</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40025</t>
+          <t>40673</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23306</t>
+          <t>23351</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41494</t>
+          <t>41366</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48997</t>
+          <t>49635</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75878</t>
+          <t>75788</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>229611</t>
+          <t>228963</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>247994</t>
+          <t>248011</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>215562</t>
+          <t>215690</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>233750</t>
+          <t>233705</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>450814</t>
+          <t>450904</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>477695</t>
+          <t>477057</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,58%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>11156</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31821</t>
+          <t>30076</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32393</t>
+          <t>31877</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>498583</t>
+          <t>539246</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48244</t>
+          <t>48126</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>709581</t>
+          <t>682632</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>46,33%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>592458</t>
+          <t>594203</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>612603</t>
+          <t>613123</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>350682</t>
+          <t>310019</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>816872</t>
+          <t>817388</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>763963</t>
+          <t>790912</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1425300</t>
+          <t>1425418</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54915</t>
+          <t>53328</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>172151</t>
+          <t>170976</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>172686</t>
+          <t>172601</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>214676</t>
+          <t>212743</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>196328</t>
+          <t>200412</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>377602</t>
+          <t>380059</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>756569</t>
+          <t>757744</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>873805</t>
+          <t>875392</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>503055</t>
+          <t>504988</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>545045</t>
+          <t>545130</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1268850</t>
+          <t>1266393</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1450124</t>
+          <t>1446040</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,83%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>211217</t>
+          <t>209116</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>305947</t>
+          <t>305479</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>423866</t>
+          <t>422326</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1213729</t>
+          <t>1190097</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>678344</t>
+          <t>678095</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1552438</t>
+          <t>1452481</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3153870</t>
+          <t>3154338</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3248600</t>
+          <t>3250701</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2498551</t>
+          <t>2522183</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3288414</t>
+          <t>3289954</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5619659</t>
+          <t>5719616</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6493753</t>
+          <t>6494002</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2C_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>66079</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90275</t>
+          <t>90180</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>97402</t>
+          <t>97007</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>120851</t>
+          <t>121820</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>169319</t>
+          <t>170053</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>205532</t>
+          <t>203487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,01%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56652</t>
+          <t>56747</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79594</t>
+          <t>80848</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45212</t>
+          <t>44243</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68661</t>
+          <t>69056</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107459</t>
+          <t>109504</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>143672</t>
+          <t>142938</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,67%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66659</t>
+          <t>64850</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97150</t>
+          <t>96542</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>125518</t>
+          <t>123585</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>162344</t>
+          <t>161613</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>199134</t>
+          <t>199069</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>249505</t>
+          <t>246836</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>188809</t>
+          <t>189417</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>219300</t>
+          <t>221109</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>191891</t>
+          <t>192622</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>228717</t>
+          <t>230650</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>390689</t>
+          <t>393358</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>441060</t>
+          <t>441125</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,9%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61679</t>
+          <t>61931</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89038</t>
+          <t>89085</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94443</t>
+          <t>95584</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>124395</t>
+          <t>123612</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>163911</t>
+          <t>162781</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>204262</t>
+          <t>204399</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,11%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>101126</t>
+          <t>101079</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128485</t>
+          <t>128233</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>101614</t>
+          <t>102397</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131566</t>
+          <t>130425</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>211911</t>
+          <t>211774</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>252262</t>
+          <t>253392</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,89%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78679</t>
+          <t>78305</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107592</t>
+          <t>106479</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105515</t>
+          <t>106885</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>135127</t>
+          <t>136504</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>192012</t>
+          <t>192733</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>233623</t>
+          <t>232656</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,36%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91517</t>
+          <t>92630</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120430</t>
+          <t>120804</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110114</t>
+          <t>108737</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>139726</t>
+          <t>138356</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>210727</t>
+          <t>211694</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>252338</t>
+          <t>251617</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,63%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23128</t>
+          <t>22221</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41869</t>
+          <t>41453</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42794</t>
+          <t>42386</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66081</t>
+          <t>66668</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70949</t>
+          <t>72140</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102189</t>
+          <t>101669</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,44%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66220</t>
+          <t>66636</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84961</t>
+          <t>85868</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83610</t>
+          <t>83023</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>106897</t>
+          <t>107305</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>155591</t>
+          <t>156111</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>186831</t>
+          <t>185640</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,01%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57163</t>
+          <t>57993</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81730</t>
+          <t>82073</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59018</t>
+          <t>59554</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85156</t>
+          <t>85918</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>125627</t>
+          <t>125345</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>160423</t>
+          <t>161257</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,31%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>80634</t>
+          <t>80291</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>105201</t>
+          <t>104371</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>93323</t>
+          <t>92561</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>119461</t>
+          <t>118925</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>180420</t>
+          <t>179586</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>215216</t>
+          <t>215498</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,22%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105573</t>
+          <t>104564</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>141429</t>
+          <t>141001</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>209874</t>
+          <t>207891</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>249844</t>
+          <t>249721</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>323198</t>
+          <t>322097</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>380874</t>
+          <t>379698</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,79%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>210082</t>
+          <t>210510</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>245938</t>
+          <t>246947</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>193090</t>
+          <t>193213</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>233060</t>
+          <t>235043</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>413571</t>
+          <t>414747</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>471247</t>
+          <t>472348</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,46%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>134109</t>
+          <t>135302</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>175516</t>
+          <t>175239</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>199026</t>
+          <t>197825</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>243422</t>
+          <t>245044</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>345990</t>
+          <t>346135</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>406147</t>
+          <t>407423</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>290586</t>
+          <t>290863</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>331993</t>
+          <t>330800</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>295290</t>
+          <t>293668</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>339686</t>
+          <t>340887</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>598667</t>
+          <t>597391</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>658824</t>
+          <t>658679</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,55%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>666019</t>
+          <t>664139</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>749273</t>
+          <t>750667</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1015276</t>
+          <t>1014719</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1109391</t>
+          <t>1108578</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1698777</t>
+          <t>1695103</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1830993</t>
+          <t>1826314</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,36%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1160953</t>
+          <t>1159559</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1244207</t>
+          <t>1246087</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1191971</t>
+          <t>1192784</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1286086</t>
+          <t>1286643</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2380595</t>
+          <t>2385274</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2512811</t>
+          <t>2516485</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,75%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77391</t>
+          <t>75417</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>104406</t>
+          <t>103694</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>127593</t>
+          <t>127229</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>155158</t>
+          <t>155755</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>209310</t>
+          <t>211003</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>248189</t>
+          <t>253317</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>65,56%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73318</t>
+          <t>74030</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100333</t>
+          <t>102307</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53525</t>
+          <t>52928</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81090</t>
+          <t>81454</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>138219</t>
+          <t>133091</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177098</t>
+          <t>175405</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,39%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>116122</t>
+          <t>114579</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>151672</t>
+          <t>152991</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>197082</t>
+          <t>196159</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>234348</t>
+          <t>232933</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>322702</t>
+          <t>321639</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>377229</t>
+          <t>374159</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,41%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>165150</t>
+          <t>163831</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>200700</t>
+          <t>202243</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>124063</t>
+          <t>125478</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>161329</t>
+          <t>162252</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>298003</t>
+          <t>301073</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>352530</t>
+          <t>353593</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,37%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91208</t>
+          <t>92529</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120667</t>
+          <t>120786</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>125392</t>
+          <t>124686</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>155491</t>
+          <t>156051</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>226384</t>
+          <t>226267</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>268734</t>
+          <t>268105</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,28%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84528</t>
+          <t>84409</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>113987</t>
+          <t>112666</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84108</t>
+          <t>83548</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114207</t>
+          <t>114913</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>176060</t>
+          <t>176689</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>218410</t>
+          <t>218527</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,13%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100612</t>
+          <t>101435</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>132703</t>
+          <t>135804</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>164483</t>
+          <t>164321</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>197335</t>
+          <t>197397</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>274659</t>
+          <t>277215</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>322726</t>
+          <t>324810</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,55%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>111063</t>
+          <t>107962</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143154</t>
+          <t>142331</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95336</t>
+          <t>95274</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>128188</t>
+          <t>128350</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>213711</t>
+          <t>211627</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>261778</t>
+          <t>259222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,32%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44270</t>
+          <t>44186</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68567</t>
+          <t>69476</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81096</t>
+          <t>83212</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107771</t>
+          <t>107737</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>133288</t>
+          <t>133474</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169802</t>
+          <t>170212</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,62%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76495</t>
+          <t>75586</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>100792</t>
+          <t>100876</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58770</t>
+          <t>58804</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>85445</t>
+          <t>83329</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>141801</t>
+          <t>141391</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>178315</t>
+          <t>178129</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73674</t>
+          <t>75450</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>101120</t>
+          <t>102498</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>102838</t>
+          <t>105945</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>132480</t>
+          <t>133380</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>185589</t>
+          <t>185717</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>224811</t>
+          <t>224830</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,12%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>74838</t>
+          <t>73460</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102284</t>
+          <t>100508</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71876</t>
+          <t>70976</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101518</t>
+          <t>98411</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>155503</t>
+          <t>155484</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>194725</t>
+          <t>194597</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>221890</t>
+          <t>222782</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>262116</t>
+          <t>263117</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>272930</t>
+          <t>272306</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>314118</t>
+          <t>313958</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>506426</t>
+          <t>504871</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>563382</t>
+          <t>565620</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,27%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>134822</t>
+          <t>133821</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>175048</t>
+          <t>174156</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>142493</t>
+          <t>142653</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>183681</t>
+          <t>184305</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>290167</t>
+          <t>287929</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>347123</t>
+          <t>348678</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,85%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>200420</t>
+          <t>199908</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>244410</t>
+          <t>245640</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>339406</t>
+          <t>337672</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>388259</t>
+          <t>385788</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>548516</t>
+          <t>550834</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>617897</t>
+          <t>617667</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,95%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>231450</t>
+          <t>230220</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>275440</t>
+          <t>275952</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>201701</t>
+          <t>204172</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>250554</t>
+          <t>252288</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>447923</t>
+          <t>448153</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>517304</t>
+          <t>514986</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,32%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1006836</t>
+          <t>1010607</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1105466</t>
+          <t>1101968</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1497883</t>
+          <t>1501790</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1594913</t>
+          <t>1599144</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2525671</t>
+          <t>2535549</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2665308</t>
+          <t>2675987</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,5%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1031860</t>
+          <t>1035358</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1130490</t>
+          <t>1126719</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>921917</t>
+          <t>917686</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1018947</t>
+          <t>1015040</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1988848</t>
+          <t>1978169</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2128485</t>
+          <t>2118607</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,52%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65824</t>
+          <t>65454</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92045</t>
+          <t>91904</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85592</t>
+          <t>87572</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115192</t>
+          <t>117627</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>158604</t>
+          <t>159126</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199098</t>
+          <t>199297</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,33%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81416</t>
+          <t>81557</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>107637</t>
+          <t>108007</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85059</t>
+          <t>82624</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>114659</t>
+          <t>112679</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174614</t>
+          <t>174415</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>215108</t>
+          <t>214586</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,42%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85510</t>
+          <t>85084</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>117640</t>
+          <t>115443</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>137368</t>
+          <t>137432</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>173767</t>
+          <t>173982</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>232851</t>
+          <t>230235</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>282968</t>
+          <t>280434</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>47,97%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>144581</t>
+          <t>146778</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>176711</t>
+          <t>177137</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>148554</t>
+          <t>148339</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>184953</t>
+          <t>184889</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>301574</t>
+          <t>304108</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>351691</t>
+          <t>354307</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,61%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56359</t>
+          <t>56770</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80409</t>
+          <t>81952</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76880</t>
+          <t>77366</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105770</t>
+          <t>105252</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>142078</t>
+          <t>141186</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>179207</t>
+          <t>178844</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,88%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97240</t>
+          <t>95697</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>121290</t>
+          <t>120879</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>106386</t>
+          <t>106904</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>135276</t>
+          <t>134790</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>210598</t>
+          <t>210961</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>247727</t>
+          <t>248619</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,78%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51882</t>
+          <t>52533</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78917</t>
+          <t>78388</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>107591</t>
+          <t>107624</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>141101</t>
+          <t>140153</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>166003</t>
+          <t>167709</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>211632</t>
+          <t>211386</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,27%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112599</t>
+          <t>113128</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>139634</t>
+          <t>138983</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>114556</t>
+          <t>115504</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>148066</t>
+          <t>148033</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>235541</t>
+          <t>235787</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>281170</t>
+          <t>279464</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,5%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67258</t>
+          <t>67773</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89818</t>
+          <t>89785</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76573</t>
+          <t>76843</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99425</t>
+          <t>100345</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>150219</t>
+          <t>151867</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>183652</t>
+          <t>184394</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>66,02%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43984</t>
+          <t>44017</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66544</t>
+          <t>66029</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46093</t>
+          <t>45173</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68945</t>
+          <t>68675</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>95668</t>
+          <t>94926</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>129101</t>
+          <t>127453</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>45,63%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53106</t>
+          <t>52468</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76108</t>
+          <t>77922</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58038</t>
+          <t>56603</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84300</t>
+          <t>84455</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>118866</t>
+          <t>118226</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>155783</t>
+          <t>154812</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,5%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>85113</t>
+          <t>83299</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>108115</t>
+          <t>108753</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>87417</t>
+          <t>87262</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>113679</t>
+          <t>115114</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>177154</t>
+          <t>178125</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>214071</t>
+          <t>214711</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>64,49%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>123452</t>
+          <t>124744</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>162455</t>
+          <t>164321</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>199235</t>
+          <t>200583</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>242667</t>
+          <t>241805</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>336338</t>
+          <t>335979</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>393226</t>
+          <t>393720</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,23%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>177823</t>
+          <t>175957</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>216826</t>
+          <t>215534</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>200835</t>
+          <t>201697</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>244267</t>
+          <t>242919</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>390554</t>
+          <t>390060</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>447442</t>
+          <t>447801</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,13%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>216158</t>
+          <t>218416</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>259990</t>
+          <t>258371</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>320062</t>
+          <t>317360</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>369165</t>
+          <t>369840</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>548823</t>
+          <t>548663</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>613389</t>
+          <t>612870</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,89%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>196790</t>
+          <t>198409</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>240622</t>
+          <t>238364</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>214734</t>
+          <t>214059</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>263837</t>
+          <t>266539</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>427290</t>
+          <t>427809</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>491856</t>
+          <t>492016</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,28%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>797796</t>
+          <t>800754</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>881605</t>
+          <t>881590</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1146440</t>
+          <t>1148280</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1247762</t>
+          <t>1246540</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1960395</t>
+          <t>1974561</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2097694</t>
+          <t>2109294</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,84%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1015323</t>
+          <t>1015338</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1099132</t>
+          <t>1096174</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1087258</t>
+          <t>1088480</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1188580</t>
+          <t>1186740</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2134254</t>
+          <t>2122654</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2271553</t>
+          <t>2257387</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,34%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11419</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19706</t>
+          <t>18697</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13940</t>
+          <t>17597</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9232</t>
+          <t>12059</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20467</t>
+          <t>24396</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25360</t>
+          <t>28571</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17986</t>
+          <t>20975</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34553</t>
+          <t>38063</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>300024</t>
+          <t>307871</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>291737</t>
+          <t>300148</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>305302</t>
+          <t>312511</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>275695</t>
+          <t>298464</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269168</t>
+          <t>291665</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280403</t>
+          <t>304002</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>575717</t>
+          <t>606335</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>566524</t>
+          <t>596843</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>583091</t>
+          <t>613931</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28666</t>
+          <t>34730</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18146</t>
+          <t>24103</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42187</t>
+          <t>49897</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63856</t>
+          <t>70956</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51226</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78400</t>
+          <t>87355</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>92521</t>
+          <t>105686</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74728</t>
+          <t>88055</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112304</t>
+          <t>126696</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>489724</t>
+          <t>495917</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>476203</t>
+          <t>480750</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500244</t>
+          <t>506544</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>451113</t>
+          <t>475538</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>436569</t>
+          <t>459139</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>463743</t>
+          <t>490197</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>940838</t>
+          <t>971455</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>921055</t>
+          <t>950445</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>958631</t>
+          <t>989086</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17142</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11214</t>
+          <t>11235</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26374</t>
+          <t>27228</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24151</t>
+          <t>23873</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16862</t>
+          <t>17028</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33875</t>
+          <t>32743</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>41293</t>
+          <t>41861</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32620</t>
+          <t>32906</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54259</t>
+          <t>54653</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>298908</t>
+          <t>298005</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>289676</t>
+          <t>288765</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>304836</t>
+          <t>304758</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>324977</t>
+          <t>332508</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>315253</t>
+          <t>323638</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332266</t>
+          <t>339353</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>623885</t>
+          <t>630514</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>610919</t>
+          <t>617722</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>632558</t>
+          <t>639469</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26815</t>
+          <t>34084</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>21318</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39915</t>
+          <t>51844</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>47556</t>
+          <t>55771</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28190</t>
+          <t>42867</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65245</t>
+          <t>69422</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>74371</t>
+          <t>89855</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51367</t>
+          <t>72804</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94883</t>
+          <t>112329</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>285742</t>
+          <t>339061</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>272642</t>
+          <t>321301</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>295840</t>
+          <t>351827</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>428162</t>
+          <t>366190</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>410473</t>
+          <t>352539</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>447528</t>
+          <t>379094</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>713903</t>
+          <t>705252</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>693391</t>
+          <t>682778</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>736907</t>
+          <t>722303</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>90,84%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14546</t>
+          <t>18246</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>11541</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24743</t>
+          <t>28150</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12362</t>
+          <t>14885</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19971</t>
+          <t>21768</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>26908</t>
+          <t>33131</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>24560</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37968</t>
+          <t>44803</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>164196</t>
+          <t>187419</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153999</t>
+          <t>177515</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169766</t>
+          <t>194124</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>246417</t>
+          <t>214033</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>238808</t>
+          <t>207150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>252545</t>
+          <t>218961</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>410613</t>
+          <t>401451</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>399553</t>
+          <t>389779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>419557</t>
+          <t>410022</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30140</t>
+          <t>31384</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21625</t>
+          <t>23003</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40673</t>
+          <t>43370</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31309</t>
+          <t>32559</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23351</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41366</t>
+          <t>42231</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>61449</t>
+          <t>63943</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49635</t>
+          <t>51873</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75788</t>
+          <t>78776</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>239496</t>
+          <t>239323</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>228963</t>
+          <t>227337</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>248011</t>
+          <t>247704</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>225747</t>
+          <t>231191</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>215690</t>
+          <t>221519</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>233705</t>
+          <t>238782</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>465243</t>
+          <t>470514</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>450904</t>
+          <t>455681</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>477057</t>
+          <t>482584</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>18990</t>
+          <t>23241</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11156</t>
+          <t>14036</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30076</t>
+          <t>34994</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>232055</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31877</t>
+          <t>29513</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>539246</t>
+          <t>50107</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>251044</t>
+          <t>61408</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48126</t>
+          <t>49376</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>682632</t>
+          <t>79319</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>605289</t>
+          <t>696446</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>594203</t>
+          <t>684693</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>613123</t>
+          <t>705651</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>617210</t>
+          <t>733890</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>310019</t>
+          <t>721950</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>817388</t>
+          <t>742544</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1222500</t>
+          <t>1430336</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>790912</t>
+          <t>1412425</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1425418</t>
+          <t>1442368</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>119798</t>
+          <t>142592</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53328</t>
+          <t>120271</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>170976</t>
+          <t>166295</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>191945</t>
+          <t>226830</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>172601</t>
+          <t>205379</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>212743</t>
+          <t>249956</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>311743</t>
+          <t>369423</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>200412</t>
+          <t>338094</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>380059</t>
+          <t>402844</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>808922</t>
+          <t>655480</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>757744</t>
+          <t>631777</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>875392</t>
+          <t>677801</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>525786</t>
+          <t>604501</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>504988</t>
+          <t>581375</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>545130</t>
+          <t>625952</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1334709</t>
+          <t>1259980</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1266393</t>
+          <t>1226559</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1446040</t>
+          <t>1291309</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>79,25%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>267516</t>
+          <t>313239</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>209116</t>
+          <t>280385</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>305479</t>
+          <t>350896</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>617174</t>
+          <t>480638</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>422326</t>
+          <t>439680</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1190097</t>
+          <t>517265</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>884690</t>
+          <t>793878</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>678095</t>
+          <t>743311</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1452481</t>
+          <t>849666</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3192301</t>
+          <t>3219523</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3154338</t>
+          <t>3181866</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3250701</t>
+          <t>3252377</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3095106</t>
+          <t>3256316</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2522183</t>
+          <t>3219689</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3289954</t>
+          <t>3297274</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6287407</t>
+          <t>6475838</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5719616</t>
+          <t>6420050</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6494002</t>
+          <t>6526405</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">

--- a/data/trans_orig/P2C_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2007 (tasa de respuesta: 99,95%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2012 (tasa de respuesta: 99,27%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2012 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2016 (tasa de respuesta: 94,57%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2016 (tasa de respuesta: 94,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
